--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Step" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Line" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Story" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1271,7 +1271,7 @@
       <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>power,pop</t>
+          <t>power</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>두 번째 판 시작: 적정 찍찍 · 인구수</t>
+          <t>두 번째 판 시작: 우리 힘 · 적정 힘</t>
         </is>
       </c>
     </row>
@@ -1718,6 +1718,194 @@
       <c r="N21" s="4" t="inlineStr">
         <is>
           <t>첫 훈장 승급 뒤: 친구들 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>g_wall</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>RoomOpen</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>RunMax</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>g_floor</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>첫 판 첫 벽 붕괴 (1층 시작 방 옆 벽 하나는 쉽게 부서짐): 계단 찾아 도망치자</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>g_pop</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>PopFull</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>RunMax</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>첫 판 최대 마릿수 도달: 인구수 표시 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>g_power_pop</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>g_power_promote,g_power_promote_new</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>첫 판에 최대 마릿수를 못 채웠으면: 여기서 인구수 표시 해금 + 설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>g_superjump</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>SuperJump</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>슈퍼 점프 처음 끝난 뒤: 신비한 힘 설명</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2027,7 +2215,11 @@
           <t>앗...! 우리들의 사랑의 결실이..!</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>baby</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -2053,7 +2245,11 @@
           <t>쥐끼리 부딪히면 가끔 새끼가 태어나 찍찍! 숫자가 많을수록 더 세게 부술 수 있어!</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>baby</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -2523,7 +2719,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>g_power</t>
+          <t>g_power_pop</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2553,7 +2749,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>g_power</t>
+          <t>g_power_pop</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -3128,6 +3324,252 @@
           <t>tab_dex</t>
         </is>
       </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>g_wall</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>labrat</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>해냈다!! 어서 계단을 찾아서 다음 층으로 도망치자!!</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>g_wall</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>벽 너머로 길이 열렸어! 계속 부수다 보면 계단 방이 나올 거야. 지도도 같이 봐!</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>minimap</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>g_pop</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>어라? 아무리 부딪혀도 새끼가 더 안 태어나잖아?!</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>g_pop</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>오른쪽 위 숫자가 지금 쥐 수 / 최대 쥐 수야. 꽉 차면 더는 번식할 수 없어!</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>g_pop</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>승급으로 쥐를 합치면 자리가 다시 생겨! 남는 쥐는 아낌없이 승급시키자!</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>g_superjump</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>labrat</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>바, 방금 뭐였어?! 쥐가 하늘 끝까지 날아올랐어!!</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>g_superjump</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>가끔 우리 몸속에 잠든 '신비한 힘'이 깨어날 때가 있어. 그게 바로 '슈퍼 점프'야!</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>g_superjump</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>하늘 끝까지 솟구쳤다가 내리꽂히면 화면 안의 물건이랑 벽까지 한꺼번에 박살 나!</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>g_superjump</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>labrat</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>언제 깨어날지는 아무도 몰라... 신비한 힘이니까! 찍!</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3442,7 +3884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3633,7 +4075,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>발동 글 값 단계가 끝나고 (필살기 등이 다 끝난 뒤) 바로</t>
+          <t>발동 글 값 단계가 끝나고 (필살기 등이 다 끝난 뒤) 바로. 쉼표로 여러 단계 (그중 하나)</t>
         </is>
       </c>
     </row>
@@ -3702,6 +4144,57 @@
       <c r="C15" s="4" t="inlineStr">
         <is>
           <t>훈장이 발동 값 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>PopFull</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>쥐 마릿수가 최대 마릿수(최대 인구)에 닿음</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>RoomOpen</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>이번 층에서 벽을 부숴 연 방이 발동 값 개 이상 (시작 방 빼고)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>SuperJump</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>이번 판 슈퍼 점프가 발동 값 번 이상 일어남 (연출이 다 끝난 뒤)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -658,7 +658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1909,6 +1909,242 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_pick</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_page</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>SkillAffordable</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n">
+        <v>202</v>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>치즈 창고 설명 뒤 치즈가 있으면: 추천 스킬 칸 강조</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_poor</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_page</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>SkillPoor</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n">
+        <v>203</v>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>치즈 창고 설명 뒤 치즈가 모자라면: 다음 판에 모아 오자</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_pick2</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>PageOpen</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_poor</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>SkillAffordable</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>치즈가 모자랐던 뒤 치즈 창고를 다시 열었고 이제 살 수 있음: 추천 스킬 칸 강조</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_buy</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SkillSelect</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_pick,l_skill_pick2</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>NotDone</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_done</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+      <c r="M29" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>살 수 있는 스킬을 골랐음: 활성화 버튼 강조</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_done</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>SkillBuy</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_pick,l_skill_pick2</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n">
+        <v>206</v>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>첫 스킬 활성화: 칭찬 + 이어진 칸 설명</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1920,7 +2156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3570,6 +3806,174 @@
         </is>
       </c>
       <c r="F59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_pick</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>치즈가 모였으니 바로 하나 찍어 보자! 반짝이는 이 칸을 눌러 봐!</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>skill_next</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_poor</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>panic</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>어라, 지금 치즈로는 아직 못 찍겠네... 다음 판에서 치즈를 더 모아 오자!</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_pick2</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>치즈가 모였네! 이제 반짝이는 이 칸을 눌러서 스킬을 찍어 보자!</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>skill_next</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_buy</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>좋아! 이제 이 '활성화' 버튼을 눌러! 치즈를 내면 스킬이 켜져.</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>skill_buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_done</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>해냈다! 다음 판부터 우리 쥐들이 더 강해질 거야!</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>l_skill_done</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>치즈가 남으면 선으로 이어진 다음 칸도 계속 찍어 봐. 이어진 칸만 열 수 있어!</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3884,7 +4288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4195,6 +4599,40 @@
       <c r="C18" s="4" t="inlineStr">
         <is>
           <t>이번 판 슈퍼 점프가 발동 값 번 이상 일어남 (연출이 다 끝난 뒤)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SkillSelect</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>치즈 창고에서 지금 살 수 있는 스킬 칸을 고름</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>SkillBuy</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>로비에 들어온 뒤 스킬을 발동 값 개 이상 활성화</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4308,7 +4746,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>그 단계를 이미 봄</t>
+          <t>그 단계를 이미 봄 (쉼표로 여러 개 = 그중 하나라도)</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4758,43 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>그 단계를 아직 안 봄</t>
+          <t>그 단계를 아직 안 봄 (쉼표로 여러 개 = 전부 안 봄)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>FloorMin</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>층이 값 이상 (Game)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SkillAffordable</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>치즈 창고 추천 스킬(지금 훈장에서 열린 칸 중 가장 싼 것)을 살 치즈가 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>SkillPoor</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>추천 스킬을 살 치즈가 모자람 (또는 살 칸이 없음)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -2156,7 +2156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3030,7 +3030,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>그리고 승급으로 높은 등급 쥐를 만들어도 찍찍이 확 올라가! 잊지 마 찍!</t>
+          <t>그리고 승급으로 높은 등급 쥐를 만들어도 찍찍이 확 올라가! 번식할 쥐만 남겨 두면 돼 찍!</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>승급으로 쥐를 합치면 자리가 다시 생겨! 남는 쥐는 아낌없이 승급시키자!</t>
+          <t>승급으로 쥐를 합치면 자리가 다시 생겨! 번식할 쥐만 남기고 나머지는 승급시키자!</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3974,6 +3974,144 @@
         </is>
       </c>
       <c r="F65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>g_promote</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>아, 그런데 조심해! 승급에 쓴 쥐들은 하나로 합쳐져서 사라져.</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>g_promote</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>panic</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>쥐가 너무 적어지면 서로 부딪힐 일이 줄어서 새끼가 거의 안 태어나!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>g_promote</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>g_power_promote_new</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>panic</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>그런데 너무 많이 합치면 쥐가 적어져서 번식이 거의 안 돼!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>g_power_promote_new</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -647,6 +647,29 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>브로커 쥐</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>tuto_broker</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>쥐구멍 암시장 상인. 상점 설명</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -658,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2145,6 +2168,322 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>l_alley</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>LobbyEnter</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>alley</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>16층 첫 클리어 뒤 로비: 맨홀 뚜껑 (지하 하수구 · 유전자 추출기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_hot</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>AlleyEnter</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>gacha</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>하수구 처음 도착: 유전자 추출기 소개</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_page</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>PageOpen</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>gacha</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>유전자 추출기 처음 열기: 뽑기 · 무료 10회 · 보장 · 천장</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>l_market</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>AlleyEnter</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n">
+        <v>310</v>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>17층 첫 클리어 뒤 뒷골목: 브로커 쥐 등장</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>l_market_lobby</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>LobbyEnter</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>NotDone</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>l_market</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>17층 클리어 뒤 아지트: 뒷골목에서 누가 부름</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>l_market_page</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>PageOpen</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n">
+        <v>311</v>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>암시장 처음 열기: 라인업 · 치즈 · 입고 · 리롤 · 고정 · 신화 천장</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>l_wish</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>PageOpen</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>gacha</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WishOpen</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_page</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>18층 클리어 뒤 유전자 추출기: 관심 종</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2156,7 +2495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4110,6 +4449,582 @@
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>promote</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>l_alley</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>찍?! 바닥 아래에서 위잉~ 하는 소리가 나!</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>l_alley</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>바닥의 맨홀 뚜껑 아래에서 나는 소리야! 뚜껑을 눌러서 지하 하수구로 내려가 보자!</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>alley_arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_hot</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>이거 봐! 연구소에서 버린 유전자 분석기를… 믹서기로 고쳐 놨어!</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>hot_gacha</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_hot</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>훔친 연구 자료를 넣으면 동료들의 유전자를 추출할 수 있어. 눌러서 열어 보자!</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>hot_gacha</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_page</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>유전자 추출기야. 연구 자료를 내면 쥐 조각이 든 캡슐이 나와!</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_page</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>처음 한 번은 10회 뽑기가 공짜야! 이 버튼부터 눌러 봐.</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>gacha_ten</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_page</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>labrat</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>panic</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>잠깐… 믹서기에 우리가 들어가는 거야?! …괜찮은 거 맞지?</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_page</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>10회 뽑기는 유니크 이상 하나가 꼭 나와. 그리고 전설이 30번, 신화가 100번 안 나오면 다음엔 무조건 나와!</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>gacha_pity</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>l_gacha_page</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>확률은 여기 다 적어 놨어. 나온 조각은 쳇바퀴 훈련에서 바로 쓸 수 있어!</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>gacha_rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>l_market_lobby</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>쉿… 맨홀 아래 하수구에서 누가 우리를 부르는데? 내려가 볼까?</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>alley_arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>l_market</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>어이~ 거기 쥐씨들. 이 몸은 연구소 지하 하수구의 브로커라고 해.</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>hot_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>l_market</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>연구소에서 빼돌린 귀한 유전자 샘플이 있지. 치즈만 넉넉하면… 흐흐.</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>hot_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>l_market_page</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>여긴 쥐구멍 암시장. 전설이랑 신화 쥐 조각만 취급한다고.</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>l_market_page</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>값은 치즈로 받지. 물건마다 종이랑 수량이 다르니 잘 골라.</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>market_slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>l_market_page</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>탈출하면서 15분쯤 지나면 새 물건이 들어와. 기다리기 싫으면 치즈를 좀 더 내고 바로 바꿔 주지.</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>market_reroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>l_market_page</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>마음에 드는 물건은 자물쇠로 하나 잡아 둬. 바꿔도 그건 안 없어지니까.</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>market_lock</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>l_market_page</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>신화가 한동안 안 들어오면… 이 몸이 어떻게든 구해 온다고. 약속하지!</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>market_pity</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>l_market_page</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>첫 거래 기념으로 선물 하나 주지. 앞으로 잘 부탁해, 흐흐.</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>l_wish</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>18층을 넘었더니 추출기를 조정할 수 있게 됐어!</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>l_wish</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>전설이랑 신화에서 원하는 친구를 하나씩 고르면, 그 등급이 나올 때 그 친구가 더 잘 나와!</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>gacha_wish</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -2195,7 +2195,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>alley</t>
+          <t>gacha</t>
         </is>
       </c>
       <c r="H31" s="4" t="n"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>16층 첫 클리어 뒤 로비: 맨홀 뚜껑 (지하 하수구 · 유전자 추출기)</t>
+          <t>16층 첫 클리어 뒤 로비: 맨홀 뚜껑 (지하 하수구 · 유전자 추출기). 맨홀은 이 단계가 시작될 때 처음 나타남 (Progress.alleyRevealStep) → 조건은 alley 가 아니라 gacha(16층 클리어)</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -448,12 +448,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
@@ -471,15 +471,20 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>화면 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>쥐 코드</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>초상화 그림 (tuto_&lt;이름&gt;_&lt;표정&gt;)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
@@ -498,15 +503,20 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>speaker_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>code_id</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>portrait</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
@@ -525,15 +535,20 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -550,17 +565,20 @@
           <t>흰 실험쥐</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="n">
+        <v>3800001</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>labrat</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>tuto_labrat</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>주인공 격. 기본 조작 · 위기 상황</t>
         </is>
@@ -577,17 +595,20 @@
           <t>안경 쥐</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="4" t="n">
+        <v>3800002</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>nerd</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>tuto_nerd</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>설명 담당. 승급 · 적정 찍찍 · 치즈 창고 · 쳇바퀴 · 훈장</t>
         </is>
@@ -604,17 +625,20 @@
           <t>시궁쥐</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="4" t="n">
+        <v>3800003</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>brownrat</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>tuto_brownrat</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>수다쟁이. 번식 · 계단 · 인구수 · 친구들</t>
         </is>
@@ -631,17 +655,20 @@
           <t>슈퍼 생쥐</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="4" t="n">
+        <v>3800004</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>hero</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>tuto_hero</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>첫 보스전 도우미 · 필살기 설명</t>
         </is>
@@ -658,13 +685,16 @@
           <t>브로커 쥐</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr"/>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>3800005</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>tuto_broker</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>쥐구멍 암시장 상인. 상점 설명</t>
         </is>
@@ -2495,7 +2525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2503,7 +2533,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="90" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2534,6 +2564,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>대사 키</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>강조할 곳</t>
         </is>
       </c>
@@ -2566,6 +2601,11 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>text_sk</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>highlight</t>
         </is>
       </c>
@@ -2597,6 +2637,11 @@
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -2626,7 +2671,10 @@
           <t>찍찍!! 큰일이다!! 어서 이 연구실을 탈출해야 해!!</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="n">
+        <v>3900001</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -2652,7 +2700,10 @@
           <t>우리 쥐들은 알아서 돌아다니면서 물건을 갉아 부숴. 부순 물건에서는 치즈가 나와!</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>3900002</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -2678,7 +2729,10 @@
           <t>화면을 클릭하면 그곳으로 모두 우르르 돌진해! 단단한 물건은 다 같이 덤벼서 부수자 찍!</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>3900003</v>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -2704,7 +2758,10 @@
           <t>화면을 끌면 여기저기 둘러볼 수 있고, 마우스 휠로 크게 볼 수도 있어.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr"/>
+      <c r="F7" s="5" t="n">
+        <v>3900004</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -2730,7 +2787,10 @@
           <t>벽을 갉으면 옆 방이 열려. 계단이 있는 방을 찾아서 계단에 닿으면 위층으로 갈 수 있어!</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="5" t="n">
+        <v>3900005</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>minimap</t>
         </is>
@@ -2760,7 +2820,10 @@
           <t>오른쪽 위 시계를 봐! 시간이 다 되면 경비원이 와서 우릴 몽땅 잡아간다고 찍!!</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="n">
+        <v>3900006</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>timer</t>
         </is>
@@ -2790,7 +2853,10 @@
           <t>앗...! 우리들의 사랑의 결실이..!</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="4" t="n">
+        <v>3900007</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>baby</t>
         </is>
@@ -2820,7 +2886,10 @@
           <t>쥐끼리 부딪히면 가끔 새끼가 태어나 찍찍! 숫자가 많을수록 더 세게 부술 수 있어!</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="n">
+        <v>3900008</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>baby</t>
         </is>
@@ -2850,7 +2919,10 @@
           <t>벌써 10마리나 모였어!</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="n">
+        <v>3900009</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -2876,7 +2948,10 @@
           <t>같은 등급 쥐가 여럿 모이면 '승급'으로 더 높은 등급 쥐로 바꿀 수 있어.</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F13" s="5" t="n">
+        <v>3900010</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -2906,7 +2981,10 @@
           <t>높은 등급 쥐는 힘이 훨씬 세다구! 왼쪽 아래 승급 버튼을 눌러 봐 찍!</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="n">
+        <v>3900011</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -2936,7 +3014,10 @@
           <t>히익!! 고, 고양이다!!</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="n">
+        <v>3900012</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -2962,7 +3043,10 @@
           <t>고양이는 쓰러뜨릴 때까지 절대 안 떠나. 다 같이 클릭해서 몰아붙여!</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="5" t="n">
+        <v>3900013</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -2988,7 +3072,10 @@
           <t>바닥에 빨간 원이 생기면 거길 곧 덮친다는 뜻이야! 한곳에 너무 몰려 있지 않게 조심해!</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="F17" s="5" t="n">
+        <v>3900014</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -3014,7 +3101,10 @@
           <t>으악! 엄청 큰 녀석이 계단을 막고 있어!!</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="n">
+        <v>3900015</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -3040,7 +3130,10 @@
           <t>보스를 쓰러뜨리기 전엔 계단을 쓸 수 없어. 체력이 줄면 이상한 필살 패턴도 쓰니까 조심해!</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>3900016</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -3066,7 +3159,10 @@
           <t>찍찍찍!! 여기선 내가 도와주지!!</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="n">
+        <v>3900017</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -3092,7 +3188,10 @@
           <t>봤지? 이게 바로 '필살기'야!</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="n">
+        <v>3900018</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -3118,7 +3217,10 @@
           <t>쳇바퀴 훈련으로 쥐를 Lv 7까지 키우면 그 쥐도 필살기를 쓸 수 있어. 게이지가 다 차면 아래 버튼으로 발동!</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr"/>
+      <c r="F22" s="5" t="n">
+        <v>3900019</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -3144,7 +3246,10 @@
           <t>그럼 건투를 빈다 찍!!</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="n">
+        <v>3900020</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -3170,7 +3275,10 @@
           <t>필살기 게이지가 다 찼어!</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="n">
+        <v>3900021</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -3196,7 +3304,10 @@
           <t>아래쪽 필살기 버튼을 눌러서 한 방 터뜨려 줘 찍!</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="4" t="n">
+        <v>3900022</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>ult</t>
         </is>
@@ -3226,7 +3337,10 @@
           <t>지난번엔 아깝게 잡혀 버렸지... 이번엔 '적정 찍찍'을 알려 줄게!</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>3900023</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -3252,7 +3366,10 @@
           <t>왼쪽 위 '찍찍!!' 숫자는 지금 우리 무리의 힘이고, 옆의 '적정'은 이 층을 넉넉히 깨려면 필요한 힘이야.</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="n">
+        <v>3900024</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>power</t>
         </is>
@@ -3282,7 +3399,10 @@
           <t>우리 힘이 적정보다 낮으면 시간 안에 계단까지 가기 힘들어!</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="F28" s="5" t="n">
+        <v>3900025</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>power</t>
         </is>
@@ -3312,7 +3432,10 @@
           <t>오른쪽 위 숫자는 지금 쥐 마릿수랑 최대 마릿수야. 최대까지만 태어날 수 있어.</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="n">
+        <v>3900026</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
@@ -3342,7 +3465,10 @@
           <t>치즈 창고에서 둥지 스킬을 찍으면 최대 마릿수가 늘어나! 쥐가 많아지면 찍찍도 쑥쑥!</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="F30" s="5" t="n">
+        <v>3900027</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
@@ -3372,7 +3498,10 @@
           <t>그리고 승급으로 높은 등급 쥐를 만들어도 찍찍이 확 올라가! 번식할 쥐만 남겨 두면 돼 찍!</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="n">
+        <v>3900028</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -3402,7 +3531,10 @@
           <t>그리고 하나 더! 같은 등급 쥐가 여럿 모이면 '승급'으로 더 높은 등급 쥐로 바꿀 수 있어.</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="F32" s="5" t="n">
+        <v>3900029</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -3432,7 +3564,10 @@
           <t>높은 등급 쥐는 힘이 훨씬 세서 찍찍이 확 올라가! 왼쪽 아래 승급 버튼을 기억해 찍!</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="n">
+        <v>3900030</v>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -3462,7 +3597,10 @@
           <t>흐어엉... 잡혀 버렸어...</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="n">
+        <v>3900031</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -3488,7 +3626,10 @@
           <t>괜찮아! 앞으론 잡히지 않게 더욱 강해지자!!</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="n">
+        <v>3900032</v>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -3514,7 +3655,10 @@
           <t>판에서 모은 치즈를 쓰면 더 강해질 수 있을 거야 찍찍!! '치즈 창고'를 열어 줄게!</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="F36" s="5" t="n">
+        <v>3900033</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
         <is>
           <t>tab_skill</t>
         </is>
@@ -3544,7 +3688,10 @@
           <t>여기가 치즈 창고야. 치즈를 써서 스킬을 하나씩 찍을 수 있어.</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>3900034</v>
+      </c>
+      <c r="G37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -3570,7 +3717,10 @@
           <t>이어진 스킬을 찍어야 다음 스킬이 열려. 높은 단계 스킬은 치즈와 함께 '연구자료'도 필요해!</t>
         </is>
       </c>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="F38" s="5" t="n">
+        <v>3900035</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>research</t>
         </is>
@@ -3600,7 +3750,10 @@
           <t>연구자료는 층을 올라갈 때마다 모여. 보스 층에선 세 배야 찍!</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>3900036</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -3626,7 +3779,10 @@
           <t>또 잡혔다아... 그래도 우리 꽤 강해졌다구!</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="n">
+        <v>3900037</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -3652,7 +3808,10 @@
           <t>이번엔 '쳇바퀴 훈련'을 열어 줄게. 판에서 모은 조각으로 쥐를 한 종씩 강화할 수 있어!</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F41" s="5" t="n">
+        <v>3900038</v>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>tab_rats</t>
         </is>
@@ -3682,7 +3841,10 @@
           <t>쥐마다 조각이 모이면 레벨을 올릴 수 있어. 레벨이 오를수록 그 쥐가 점점 세져!</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>3900039</v>
+      </c>
+      <c r="G42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -3708,7 +3870,10 @@
           <t>Lv 3이 되면 그 쥐만의 특수 액션, Lv 7이 되면 필살기가 열려!</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="F43" s="5" t="n">
+        <v>3900040</v>
+      </c>
+      <c r="G43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -3734,7 +3899,10 @@
           <t>필살기... 기억나지? 찍찍!!</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="n">
+        <v>3900041</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -3760,7 +3928,10 @@
           <t>앗! 더 이상 강해질 수가 없어 찍!!</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="n">
+        <v>3900042</v>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -3786,7 +3957,10 @@
           <t>그렇다면.... 이때까지 모은 연구의 성과를!! 찍찍!!</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>3900043</v>
+      </c>
+      <c r="G46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -3812,7 +3986,10 @@
           <t>'찍찍!! 훈장'을 열어 줄게. 훈장을 올리면 새로운 스킬들이 열려!</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="F47" s="5" t="n">
+        <v>3900044</v>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
         <is>
           <t>tab_rank</t>
         </is>
@@ -3842,7 +4019,10 @@
           <t>훈장을 올리려면 연구자료와 함께 몇 가지 조건이 필요해. 조건은 여기서 확인할 수 있어!</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="F48" s="5" t="n">
+        <v>3900045</v>
+      </c>
+      <c r="G48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -3868,7 +4048,10 @@
           <t>찍찍 훈장을 얻으면 친구들도 늘어날 거야 찍찍!!</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="n">
+        <v>3900046</v>
+      </c>
+      <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -3894,7 +4077,10 @@
           <t>'친구들!!'에서 지금까지 만난 친구들을 볼 수 있어!</t>
         </is>
       </c>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="F50" s="4" t="n">
+        <v>3900047</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>tab_dex</t>
         </is>
@@ -3924,7 +4110,10 @@
           <t>해냈다!! 어서 계단을 찾아서 다음 층으로 도망치자!!</t>
         </is>
       </c>
-      <c r="F51" s="4" t="n"/>
+      <c r="F51" s="4" t="n">
+        <v>3900048</v>
+      </c>
+      <c r="G51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -3950,7 +4139,10 @@
           <t>벽 너머로 길이 열렸어! 계속 부수다 보면 계단 방이 나올 거야. 지도도 같이 봐!</t>
         </is>
       </c>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="F52" s="4" t="n">
+        <v>3900049</v>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>minimap</t>
         </is>
@@ -3980,7 +4172,10 @@
           <t>어라? 아무리 부딪혀도 새끼가 더 안 태어나잖아?!</t>
         </is>
       </c>
-      <c r="F53" s="4" t="n"/>
+      <c r="F53" s="4" t="n">
+        <v>3900050</v>
+      </c>
+      <c r="G53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -4006,7 +4201,10 @@
           <t>오른쪽 위 숫자가 지금 쥐 수 / 최대 쥐 수야. 꽉 차면 더는 번식할 수 없어!</t>
         </is>
       </c>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="F54" s="4" t="n">
+        <v>3900051</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>pop</t>
         </is>
@@ -4036,7 +4234,10 @@
           <t>승급으로 쥐를 합치면 자리가 다시 생겨! 번식할 쥐만 남기고 나머지는 승급시키자!</t>
         </is>
       </c>
-      <c r="F55" s="4" t="inlineStr">
+      <c r="F55" s="4" t="n">
+        <v>3900052</v>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -4066,7 +4267,10 @@
           <t>바, 방금 뭐였어?! 쥐가 하늘 끝까지 날아올랐어!!</t>
         </is>
       </c>
-      <c r="F56" s="4" t="n"/>
+      <c r="F56" s="4" t="n">
+        <v>3900053</v>
+      </c>
+      <c r="G56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -4092,7 +4296,10 @@
           <t>가끔 우리 몸속에 잠든 '신비한 힘'이 깨어날 때가 있어. 그게 바로 '슈퍼 점프'야!</t>
         </is>
       </c>
-      <c r="F57" s="4" t="n"/>
+      <c r="F57" s="4" t="n">
+        <v>3900054</v>
+      </c>
+      <c r="G57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -4118,7 +4325,10 @@
           <t>하늘 끝까지 솟구쳤다가 내리꽂히면 화면 안의 물건이랑 벽까지 한꺼번에 박살 나!</t>
         </is>
       </c>
-      <c r="F58" s="4" t="n"/>
+      <c r="F58" s="4" t="n">
+        <v>3900055</v>
+      </c>
+      <c r="G58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -4144,7 +4354,10 @@
           <t>언제 깨어날지는 아무도 몰라... 신비한 힘이니까! 찍!</t>
         </is>
       </c>
-      <c r="F59" s="4" t="n"/>
+      <c r="F59" s="4" t="n">
+        <v>3900056</v>
+      </c>
+      <c r="G59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -4170,7 +4383,10 @@
           <t>치즈가 모였으니 바로 하나 찍어 보자! 반짝이는 이 칸을 눌러 봐!</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F60" s="4" t="n">
+        <v>3900057</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>skill_next</t>
         </is>
@@ -4200,7 +4416,10 @@
           <t>어라, 지금 치즈로는 아직 못 찍겠네... 다음 판에서 치즈를 더 모아 오자!</t>
         </is>
       </c>
-      <c r="F61" s="4" t="n"/>
+      <c r="F61" s="4" t="n">
+        <v>3900058</v>
+      </c>
+      <c r="G61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -4226,7 +4445,10 @@
           <t>치즈가 모였네! 이제 반짝이는 이 칸을 눌러서 스킬을 찍어 보자!</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
+      <c r="F62" s="4" t="n">
+        <v>3900059</v>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
         <is>
           <t>skill_next</t>
         </is>
@@ -4256,7 +4478,10 @@
           <t>좋아! 이제 이 '활성화' 버튼을 눌러! 치즈를 내면 스킬이 켜져.</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F63" s="4" t="n">
+        <v>3900060</v>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>skill_buy</t>
         </is>
@@ -4286,7 +4511,10 @@
           <t>해냈다! 다음 판부터 우리 쥐들이 더 강해질 거야!</t>
         </is>
       </c>
-      <c r="F64" s="4" t="n"/>
+      <c r="F64" s="4" t="n">
+        <v>3900061</v>
+      </c>
+      <c r="G64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -4312,7 +4540,10 @@
           <t>치즈가 남으면 선으로 이어진 다음 칸도 계속 찍어 봐. 이어진 칸만 열 수 있어!</t>
         </is>
       </c>
-      <c r="F65" s="4" t="n"/>
+      <c r="F65" s="4" t="n">
+        <v>3900062</v>
+      </c>
+      <c r="G65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -4338,7 +4569,10 @@
           <t>아, 그런데 조심해! 승급에 쓴 쥐들은 하나로 합쳐져서 사라져.</t>
         </is>
       </c>
-      <c r="F66" s="4" t="n"/>
+      <c r="F66" s="4" t="n">
+        <v>3900063</v>
+      </c>
+      <c r="G66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -4364,7 +4598,10 @@
           <t>쥐가 너무 적어지면 서로 부딪힐 일이 줄어서 새끼가 거의 안 태어나!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
         </is>
       </c>
-      <c r="F67" s="4" t="n"/>
+      <c r="F67" s="4" t="n">
+        <v>3900064</v>
+      </c>
+      <c r="G67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -4390,7 +4627,10 @@
           <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F68" s="4" t="n">
+        <v>3900065</v>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -4420,7 +4660,10 @@
           <t>그런데 너무 많이 합치면 쥐가 적어져서 번식이 거의 안 돼!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
         </is>
       </c>
-      <c r="F69" s="4" t="n"/>
+      <c r="F69" s="4" t="n">
+        <v>3900066</v>
+      </c>
+      <c r="G69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -4446,7 +4689,10 @@
           <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F70" s="4" t="n">
+        <v>3900065</v>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
@@ -4476,7 +4722,10 @@
           <t>찍?! 바닥 아래에서 위잉~ 하는 소리가 나!</t>
         </is>
       </c>
-      <c r="F71" s="4" t="n"/>
+      <c r="F71" s="4" t="n">
+        <v>3900068</v>
+      </c>
+      <c r="G71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -4502,7 +4751,10 @@
           <t>바닥의 맨홀 뚜껑 아래에서 나는 소리야! 뚜껑을 눌러서 지하 하수구로 내려가 보자!</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F72" s="4" t="n">
+        <v>3900069</v>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>alley_arrow</t>
         </is>
@@ -4532,7 +4784,10 @@
           <t>이거 봐! 연구소에서 버린 유전자 분석기를… 믹서기로 고쳐 놨어!</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr">
+      <c r="F73" s="4" t="n">
+        <v>3900070</v>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>hot_gacha</t>
         </is>
@@ -4562,7 +4817,10 @@
           <t>훔친 연구 자료를 넣으면 동료들의 유전자를 추출할 수 있어. 눌러서 열어 보자!</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F74" s="4" t="n">
+        <v>3900071</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>hot_gacha</t>
         </is>
@@ -4592,7 +4850,10 @@
           <t>유전자 추출기야. 연구 자료를 내면 쥐 조각이 든 캡슐이 나와!</t>
         </is>
       </c>
-      <c r="F75" s="4" t="n"/>
+      <c r="F75" s="4" t="n">
+        <v>3900072</v>
+      </c>
+      <c r="G75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -4618,7 +4879,10 @@
           <t>처음 한 번은 10회 뽑기가 공짜야! 이 버튼부터 눌러 봐.</t>
         </is>
       </c>
-      <c r="F76" s="4" t="inlineStr">
+      <c r="F76" s="4" t="n">
+        <v>3900073</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
         <is>
           <t>gacha_ten</t>
         </is>
@@ -4648,7 +4912,10 @@
           <t>잠깐… 믹서기에 우리가 들어가는 거야?! …괜찮은 거 맞지?</t>
         </is>
       </c>
-      <c r="F77" s="4" t="n"/>
+      <c r="F77" s="4" t="n">
+        <v>3900074</v>
+      </c>
+      <c r="G77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -4674,7 +4941,10 @@
           <t>10회 뽑기는 유니크 이상 하나가 꼭 나와. 그리고 전설이 30번, 신화가 100번 안 나오면 다음엔 무조건 나와!</t>
         </is>
       </c>
-      <c r="F78" s="4" t="inlineStr">
+      <c r="F78" s="4" t="n">
+        <v>3900075</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
         <is>
           <t>gacha_pity</t>
         </is>
@@ -4704,7 +4974,10 @@
           <t>확률은 여기 다 적어 놨어. 나온 조각은 쳇바퀴 훈련에서 바로 쓸 수 있어!</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F79" s="4" t="n">
+        <v>3900076</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>gacha_rates</t>
         </is>
@@ -4734,7 +5007,10 @@
           <t>쉿… 맨홀 아래 하수구에서 누가 우리를 부르는데? 내려가 볼까?</t>
         </is>
       </c>
-      <c r="F80" s="4" t="inlineStr">
+      <c r="F80" s="4" t="n">
+        <v>3900077</v>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>alley_arrow</t>
         </is>
@@ -4764,7 +5040,10 @@
           <t>어이~ 거기 쥐씨들. 이 몸은 연구소 지하 하수구의 브로커라고 해.</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F81" s="4" t="n">
+        <v>3900078</v>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
         <is>
           <t>hot_market</t>
         </is>
@@ -4794,7 +5073,10 @@
           <t>연구소에서 빼돌린 귀한 유전자 샘플이 있지. 치즈만 넉넉하면… 흐흐.</t>
         </is>
       </c>
-      <c r="F82" s="4" t="inlineStr">
+      <c r="F82" s="4" t="n">
+        <v>3900079</v>
+      </c>
+      <c r="G82" s="4" t="inlineStr">
         <is>
           <t>hot_market</t>
         </is>
@@ -4824,7 +5106,10 @@
           <t>여긴 쥐구멍 암시장. 전설이랑 신화 쥐 조각만 취급한다고.</t>
         </is>
       </c>
-      <c r="F83" s="4" t="n"/>
+      <c r="F83" s="4" t="n">
+        <v>3900080</v>
+      </c>
+      <c r="G83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -4850,7 +5135,10 @@
           <t>값은 치즈로 받지. 물건마다 종이랑 수량이 다르니 잘 골라.</t>
         </is>
       </c>
-      <c r="F84" s="4" t="inlineStr">
+      <c r="F84" s="4" t="n">
+        <v>3900081</v>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>market_slot</t>
         </is>
@@ -4880,7 +5168,10 @@
           <t>탈출하면서 15분쯤 지나면 새 물건이 들어와. 기다리기 싫으면 치즈를 좀 더 내고 바로 바꿔 주지.</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F85" s="4" t="n">
+        <v>3900082</v>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
         <is>
           <t>market_reroll</t>
         </is>
@@ -4910,7 +5201,10 @@
           <t>마음에 드는 물건은 자물쇠로 하나 잡아 둬. 바꿔도 그건 안 없어지니까.</t>
         </is>
       </c>
-      <c r="F86" s="4" t="inlineStr">
+      <c r="F86" s="4" t="n">
+        <v>3900083</v>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
         <is>
           <t>market_lock</t>
         </is>
@@ -4940,7 +5234,10 @@
           <t>신화가 한동안 안 들어오면… 이 몸이 어떻게든 구해 온다고. 약속하지!</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F87" s="4" t="n">
+        <v>3900084</v>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
         <is>
           <t>market_pity</t>
         </is>
@@ -4970,7 +5267,10 @@
           <t>첫 거래 기념으로 선물 하나 주지. 앞으로 잘 부탁해, 흐흐.</t>
         </is>
       </c>
-      <c r="F88" s="4" t="n"/>
+      <c r="F88" s="4" t="n">
+        <v>3900085</v>
+      </c>
+      <c r="G88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -4996,7 +5296,10 @@
           <t>18층을 넘었더니 추출기를 조정할 수 있게 됐어!</t>
         </is>
       </c>
-      <c r="F89" s="4" t="n"/>
+      <c r="F89" s="4" t="n">
+        <v>3900086</v>
+      </c>
+      <c r="G89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -5022,7 +5325,10 @@
           <t>전설이랑 신화에서 원하는 친구를 하나씩 고르면, 그 등급이 나올 때 그 친구가 더 잘 나와!</t>
         </is>
       </c>
-      <c r="F90" s="4" t="inlineStr">
+      <c r="F90" s="4" t="n">
+        <v>3900087</v>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
         <is>
           <t>gacha_wish</t>
         </is>
@@ -5039,13 +5345,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5069,6 +5376,11 @@
           <t>대사</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>대사 키</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -5091,6 +5403,11 @@
           <t>text</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>text_sk</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -5111,6 +5428,11 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -5131,6 +5453,9 @@
           <t>찍... 찍찍찍...! (우리들은 그저 이곳이 낙원인 줄만 알고 있었지...)</t>
         </is>
       </c>
+      <c r="E4" s="5" t="n">
+        <v>4000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -5149,6 +5474,9 @@
           <t>찍찍! 찍~ (매일 치즈가 나오고, 쳇바퀴는 언제나 돌아갔으니까.)</t>
         </is>
       </c>
+      <c r="E5" s="5" t="n">
+        <v>4000002</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -5167,6 +5495,9 @@
           <t>찍찍...! (가끔 하늘에서 '손가락'이 내려왔어.)</t>
         </is>
       </c>
+      <c r="E6" s="4" t="n">
+        <v>4000003</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -5185,6 +5516,9 @@
           <t>찍~ 찍찍! (손가락의 은총을 받은 친구는 더 좋은 곳으로 간다고 믿었지.)</t>
         </is>
       </c>
+      <c r="E7" s="5" t="n">
+        <v>4000004</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -5203,6 +5537,9 @@
           <t>찍...? (그런데... 은총을 받은 친구들은 다시는 돌아오지 않았어.)</t>
         </is>
       </c>
+      <c r="E8" s="5" t="n">
+        <v>4000005</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -5221,6 +5558,9 @@
           <t>찍찍찍찍...! (우리는 모이면 모일수록 똑똑해졌고...)</t>
         </is>
       </c>
+      <c r="E9" s="5" t="n">
+        <v>4000006</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -5239,6 +5579,9 @@
           <t>찍!!! (결국 알아 버렸어. 우리가... 실험당하고 있다는 걸!!)</t>
         </is>
       </c>
+      <c r="E10" s="5" t="n">
+        <v>4000007</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -5257,6 +5600,9 @@
           <t>찍... 찍찍찍... (그날, 쥐류는 떠올렸다...)</t>
         </is>
       </c>
+      <c r="E11" s="4" t="n">
+        <v>4000008</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -5275,6 +5621,9 @@
           <t>찍찍... 찍...!! (놈들에게 지배당하던 공포를... 철창 속에 갇혀 있던 굴욕을...!!)</t>
         </is>
       </c>
+      <c r="E12" s="5" t="n">
+        <v>4000009</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -5293,6 +5642,9 @@
           <t>찍찍!! (이대로 있을 순 없어!)</t>
         </is>
       </c>
+      <c r="E13" s="4" t="n">
+        <v>4000010</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -5311,6 +5663,9 @@
           <t>찍찍찍!!! (힘을 모아서 이 연구실을 탈출하자!!)</t>
         </is>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>4000011</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -5328,6 +5683,9 @@
         <is>
           <t>찍!찍!!찍!!! (사람과 고양이의 방해를 뚫고... 반드시 탈출하는 거야!!)</t>
         </is>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4000012</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1848,12 +1848,12 @@
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>RunMax</t>
+          <t>NotDone</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>g_pop_f5,g_power_pop</t>
         </is>
       </c>
       <c r="H23" s="4" t="n"/>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>첫 판 최대 마릿수 도달: 인구수 표시 해금</t>
+          <t>최대 마릿수에 처음 닿음 (몇 번째 판이든). 이미 g_pop_f5 · g_power_pop 으로 설명했으면 안 나옴 (사용자 2026-10-13: 완료 스위치 하나)</t>
         </is>
       </c>
     </row>
@@ -2511,6 +2511,54 @@
       <c r="N37" s="4" t="inlineStr">
         <is>
           <t>18층 클리어 뒤 유전자 추출기: 관심 종</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_f5</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>FloorStart</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>NotDone</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>g_pop,g_power_pop</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+      <c r="M38" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>4층을 깰 때까지 최대 마릿수에 닿은 적이 없으면 5층에 올라간 순간 (g_pop · g_power_pop 안 봄): 최대 마릿수 설명 (사용자 2026-10-13)</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5331,6 +5379,101 @@
       <c r="G90" s="4" t="inlineStr">
         <is>
           <t>gacha_wish</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_f5</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>벌써 5층이야! 그런데 쥐는 끝없이 늘어나는 게 아니래.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>3900088</v>
+      </c>
+      <c r="G91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_f5</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>오른쪽 위 숫자가 지금 쥐 수 / 최대 쥐 수야. 꽉 차면 더는 번식할 수 없어!</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>3900051</v>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_f5</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>꽉 찼을 땐 승급으로 쥐를 합치면 자리가 다시 생겨! 번식할 쥐만 남기고 나머지는 승급시키자!</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>3900090</v>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -968,14 +968,10 @@
       <c r="E4" s="4" t="inlineStr"/>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>RunMax</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>InRound</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr"/>
       <c r="J4" s="4" t="inlineStr"/>
@@ -986,7 +982,7 @@
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>첫 판 1층 시작: 탈출 목표 · 자동 파괴 · 클릭 돌진 · 화면 이동</t>
+          <t>튜토리얼 라운드 1층 시작: 탈출 목표 · 자동 파괴 · 클릭 돌진 · 화면 이동 (2026-10-15: 첫 판 → 라운드 동안)</t>
         </is>
       </c>
     </row>
@@ -1003,33 +999,29 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>FloorTime</t>
+          <t>Hurry</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>RunMax</t>
+          <t>FloorMin</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>g_intro</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr"/>
@@ -1038,7 +1030,7 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>1층 12초: 벽 · 계단 · 제한시간</t>
+          <t>2층부터: 남은 제한시간 30초 또는 계단 방 벽 체력 30% 이하(열려도) 중 먼저 → 제한시간 안내 (2026-10-15, 한 번만)</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1056,12 @@
       <c r="E6" s="4" t="inlineStr"/>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>RunMax</t>
+          <t>FloorMin</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -1082,7 +1074,7 @@
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>첫 탄생: 번식</t>
+          <t>첫 탄생: 번식 (튜토리얼 라운드 동안 1층은 번식 없음 → 2층 첫 번식, 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1100,12 @@
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>RunMax</t>
+          <t>FloorMin</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
@@ -1130,7 +1122,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>10마리: 승급 해금</t>
+          <t>2층부터 처음 10마리: 승급 해금 (2026-10-15: 첫 판 → 2층)</t>
         </is>
       </c>
     </row>
@@ -1154,8 +1146,16 @@
         <v>0</v>
       </c>
       <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>FloorMin</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr"/>
       <c r="J8" s="4" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>고양이 처음 등장</t>
+          <t>고양이 처음 등장 (안내 전엔 1층 고양이 없음 · 2층부터 층 들어오고 30초 뒤 반드시 등장 = StageManager.tutoCatDelay)</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>RunMin</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>l_first</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>두 번째 판 시작: 우리 힘 · 적정 힘</t>
+          <t>튜토리얼 라운드 + 첫 치즈 창고(l_first) 다음 판 시작: 우리 힘 · 적정 힘 (2026-10-15: 두 번째 판 → l_first 다음 판)</t>
         </is>
       </c>
     </row>
@@ -1460,14 +1460,10 @@
       <c r="E15" s="4" t="inlineStr"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>RunMin</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>RoundDone</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="inlineStr"/>
       <c r="I15" s="4" t="inlineStr"/>
       <c r="J15" s="4" t="inlineStr">
@@ -1482,7 +1478,7 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>첫 게임 오버 뒤 로비: 치즈 창고 해금</t>
+          <t>튜토리얼 라운드(1·2층 안내)를 다 본 뒤 로비: 치즈 창고 해금 (2026-10-15: 라운드 중 게임 오버·포기면 안 열림)</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1552,12 @@
       <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>RunMin</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>g_power</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1586,7 +1582,7 @@
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>두 번째 게임 오버 뒤: 쳇바퀴 훈련 해금</t>
+          <t>l_first 다음 판(g_power)을 하고 온 로비: 쳇바퀴 훈련 해금</t>
         </is>
       </c>
     </row>
@@ -1675,14 +1671,22 @@
           <t>rank</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>OpenPage</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
       <c r="M19" s="4" t="n">
         <v>220</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>첫 훈장 트리 다 찍고 승급 조건 충족: 찍찍!! 훈장 해금</t>
+          <t>첫 훈장 트리 다 찍고 승급 조건 충족: 찍찍!! 훈장 해금 → 끝나면 훈장 페이지 열기 (치즈 창고 훈장 버튼도 여기로 보냄)</t>
         </is>
       </c>
     </row>
@@ -1796,14 +1800,10 @@
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>RunMax</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>InRound</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Done</t>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>g_floor</t>
+          <t>g_intro</t>
         </is>
       </c>
       <c r="J22" s="4" t="n"/>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>첫 판 첫 벽 붕괴 (1층 시작 방 옆 벽 하나는 쉽게 부서짐): 계단 찾아 도망치자</t>
+          <t>튜토리얼 라운드 1층 첫 벽 붕괴 (시작 방 옆 벽 하나는 쉽게 부서짐): 계단 찾아 도망치자 + 맵 안내 (2026-10-15: 맵 안내 g_floor → 여기로)</t>
         </is>
       </c>
     </row>
@@ -2813,11 +2813,11 @@
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>g_floor</t>
+          <t>g_wall</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -4165,7 +4165,7 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6187,6 +6187,23 @@
       <c r="C20" s="4" t="inlineStr">
         <is>
           <t>로비에 들어온 뒤 스킬을 발동 값 개 이상 활성화</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Hurry</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>남은 제한시간이 발동 값 초 이하 · 또는 계단 방 벽(가장 깎인 것)이 발동 글 값 비율 이하 (계단 방이 열려도 발동)</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6349,6 +6366,30 @@
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>추천 스킬을 살 치즈가 모자람 (또는 살 칸이 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>RoundDone</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>튜토리얼 라운드(Progress.TutoRoundSteps: 1·2층 안내)를 다 봄</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>InRound</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>튜토리얼 라운드 중</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2562,6 +2562,90 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>l_rats_ult</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>l_rats_page</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>g_boss_ult</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+      <c r="M39" s="4" t="n">
+        <v>212</v>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>쳇바퀴 훈련 페이지 안내 뒤: 첫 보스 필살기 시연(g_boss_ult)을 본 경우에만 "필살기 기억나지?" (2026-10-17: 못 봤는데 언급하던 것)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>g_super</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>SuperReady</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>초필살기 버튼이 처음 뜸 (신화 · 쳇바퀴 Lv 10 · 필살기 5번, 2026-10-18)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2573,7 +2657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3929,7 +4013,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>l_rats_page</t>
+          <t>l_rats_ult</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -5474,6 +5558,68 @@
       <c r="G93" s="4" t="inlineStr">
         <is>
           <t>promote</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>g_super</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>우와! 신화 친구가 필살기를 다섯 번이나 써서 힘이 넘쳐흘러!</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>3900092</v>
+      </c>
+      <c r="G94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>g_super</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>아래 반짝이는 '초필살기' 버튼을 눌러 봐! 종마다 한 판에 한 번뿐이야 찍!!</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>3900093</v>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>super</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Step" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Line" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Story" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2646,6 +2646,230 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>g_aug</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>AugPick</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+      <c r="M41" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>증강 고르기 창이 처음 뜸 (31층 이상 클리어, 2026-10-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>g_aug_manage</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>g_aug</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+      <c r="M42" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>증강 첫 고르기 안내 뒤: 슬롯·Tab 관리 창</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>l_aug</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>LobbyEnter</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>aug</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>aug</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+      <c r="M43" s="4" t="n">
+        <v>240</v>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>31층 도달 뒤 로비: 지하 증강 연구소 소개 (건물 해금)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>l_aug_page</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>PageOpen</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>aug</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>l_aug</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+      <c r="M44" s="4" t="n">
+        <v>241</v>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>증강 연구소 페이지 처음 열림: 합성 · 강화 · 도감</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>l_aug_carry</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>LobbyEnter</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>aug_carry</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>l_aug</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+      <c r="M45" s="4" t="n">
+        <v>242</v>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>41층 도달 뒤 로비: 증강 1개 들고 가기</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2657,7 +2881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5620,6 +5844,262 @@
       <c r="G95" s="4" t="inlineStr">
         <is>
           <t>super</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>g_aug</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>hero</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>여기서부턴 층을 넘을 때마다 '증강'을 하나 고를 수 있지! 마음에 드는 걸 골라라!</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>3900094</v>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>augpick</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>g_aug_manage</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>고른 증강은 이번 판 동안 슬롯에 끼워져서 바로 효과가 나! 슬롯은 5칸이야.</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>3900095</v>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>augbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>g_aug_manage</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>얻은 증강은 전부 지하 '증강 연구소'에 쌓여! 판 중에도 Tab 을 누르면 보관함이랑 바꿔 낄 수 있어.</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>3900096</v>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>augbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>l_aug</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>어이, 지하에 새 가게가 들어섰다구. 이름하여 '증강 연구소'!</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>3900097</v>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>l_aug</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>모은 증강을 구경하고, 같은 등급끼리 합성해서 더 좋은 놈을 노려 봐. 대신 꽝이 나올 수도 있다구?</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>3900098</v>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>aug</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>l_aug_page</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>판에서 끼고 층을 넘은 증강엔 강화 포인트가 쌓여. 포인트랑 치즈를 내면 효과가 조금씩 세진다구.</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>3900099</v>
+      </c>
+      <c r="G101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>l_aug_page</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>합성 재료로 쓴 증강은 강화도 같이 사라지니까 아끼는 놈은 조심하라구!</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>3900100</v>
+      </c>
+      <c r="G102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>l_aug_carry</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>41층까지 왔다고? 이제 연구소에서 증강 하나를 '들고 가기'로 정하면 1층부터 끼고 출발할 수 있다구!</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>3900101</v>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>aug</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1091,38 +1091,46 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>RatCount</t>
+          <t>PopFull</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>FloorMin</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
+          <t>g_pop_f5,g_power_pop</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
           <t>promote</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>2층부터 처음 10마리: 승급 해금 (2026-10-15: 첫 판 → 2층)</t>
+          <t>최대 마릿수를 미리 설명(g_pop_f5 · g_power_pop)한 뒤 처음 꽉 참: 승급 해금 + 설명 (2026-10-21: 10마리 → 최대 마릿수 도달과 함께. 초반엔 승급이 없어서 꽉 채우도록 유도)</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1397,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>g_power_promote_new</t>
+          <t>g_power_hint</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1407,7 +1415,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>g_power</t>
+          <t>g_power,g_power_pop</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1420,21 +1428,25 @@
           <t>promote</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
-      <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>promote</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>첫 판에 승급을 못 열었으면: 여기서 승급 해금 + 설명</t>
+          <t>적정 설명(+ 인구수 설명) 뒤 아직 승급이 잠겨 있으면: 최대 마릿수까지 꽉 채우면 승급이 열린다고 예고 (2026-10-21: g_power_promote_new 의 승급 해금을 없애고 예고로)</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1882,7 @@
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>최대 마릿수에 처음 닿음 (몇 번째 판이든). 이미 g_pop_f5 · g_power_pop 으로 설명했으면 안 나옴 (사용자 2026-10-13: 완료 스위치 하나)</t>
+          <t>최대 마릿수에 처음 닿음 (몇 번째 판이든). 이미 g_pop_f5 · g_power_pop 으로 설명했으면 안 나옴 (사용자 2026-10-13: 완료 스위치 하나). 끝나면 바로 g_pop_promote (승급 해금, 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1907,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>g_power_promote,g_power_promote_new</t>
+          <t>g_power,g_power_promote</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1922,7 +1934,7 @@
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>첫 판에 최대 마릿수를 못 채웠으면: 여기서 인구수 표시 해금 + 설명</t>
+          <t>적정 설명 때 인구수 표시가 아직 잠겨 있으면: 여기서 인구수 표시 해금 + 설명 (2026-10-21: 승급 이어짐 대신 g_power 바로 뒤 · 그다음 g_power_hint)</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2570,7 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>4층을 깰 때까지 최대 마릿수에 닿은 적이 없으면 5층에 올라간 순간 (g_pop · g_power_pop 안 봄): 최대 마릿수 설명 (사용자 2026-10-13)</t>
+          <t>4층을 깰 때까지 최대 마릿수에 닿은 적이 없으면 5층에 올라간 순간 (g_pop · g_power_pop 안 봄): 최대 마릿수 설명 + "꽉 채우면 승급을 알려 줄게" (사용자 2026-10-13 · 승급 예고 2026-10-21). 승급은 꽉 찼을 때 g_promote</t>
         </is>
       </c>
     </row>
@@ -2867,6 +2879,58 @@
       <c r="N45" s="4" t="inlineStr">
         <is>
           <t>41층 도달 뒤 로비: 증강 1개 들고 가기</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_promote</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>g_pop</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>g_pop 바로 뒤: 꽉 찼을 땐 승급 → 승급 해금 + 설명 (2026-10-21: 승급은 최대 마릿수 도달과 함께)</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3272,13 +3336,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>벌써 10마리나 모였어!</t>
+          <t>드디어 최대 마릿수까지 꽉 찼어! 약속대로 '승급'을 알려 줄게!</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
         <v>3900009</v>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -3334,7 +3402,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>높은 등급 쥐는 힘이 훨씬 세다구! 왼쪽 아래 승급 버튼을 눌러 봐 찍!</t>
+          <t>합친 만큼 자리가 생겨서 다시 번식할 수 있고, 높은 등급 쥐는 힘도 훨씬 세다구! 왼쪽 아래 승급 버튼을 눌러 봐 찍!</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
@@ -3869,7 +3937,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>g_power_promote_new</t>
+          <t>g_power_hint</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3884,7 +3952,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>그리고 하나 더! 같은 등급 쥐가 여럿 모이면 '승급'으로 더 높은 등급 쥐로 바꿀 수 있어.</t>
+          <t>적정 찍찍이 모자랄 땐 쥐를 최대 마릿수까지 꽉 채워 봐!</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -3892,7 +3960,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>promote</t>
+          <t>pop</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3970,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>g_power_promote_new</t>
+          <t>g_power_hint</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3917,7 +3985,7 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>높은 등급 쥐는 힘이 훨씬 세서 찍찍이 확 올라가! 왼쪽 아래 승급 버튼을 기억해 찍!</t>
+          <t>꽉 차면 쥐를 더 센 쥐로 바꾸는 '승급'이 열릴 거야. 그럼 찍찍이 확 올라가 찍!</t>
         </is>
       </c>
       <c r="F33" s="5" t="n">
@@ -3925,7 +3993,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>promote</t>
+          <t>pop</t>
         </is>
       </c>
     </row>
@@ -4568,40 +4636,36 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>g_pop</t>
+          <t>g_superjump</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>labrat</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>승급으로 쥐를 합치면 자리가 다시 생겨! 번식할 쥐만 남기고 나머지는 승급시키자!</t>
+          <t>바, 방금 뭐였어?! 쥐가 하늘 끝까지 날아올랐어!!</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3900052</v>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>promote</t>
-        </is>
-      </c>
+        <v>3900053</v>
+      </c>
+      <c r="G55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
@@ -4610,27 +4674,27 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>labrat</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>바, 방금 뭐였어?! 쥐가 하늘 끝까지 날아올랐어!!</t>
+          <t>가끔 우리 몸속에 잠든 '신비한 힘'이 깨어날 때가 있어. 그게 바로 '슈퍼 점프'야!</t>
         </is>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3900053</v>
+        <v>3900054</v>
       </c>
       <c r="G56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
@@ -4644,22 +4708,22 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>가끔 우리 몸속에 잠든 '신비한 힘'이 깨어날 때가 있어. 그게 바로 '슈퍼 점프'야!</t>
+          <t>하늘 끝까지 솟구쳤다가 내리꽂히면 화면 안의 물건이랑 벽까지 한꺼번에 박살 나!</t>
         </is>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3900054</v>
+        <v>3900055</v>
       </c>
       <c r="G57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
@@ -4668,36 +4732,36 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>labrat</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>하늘 끝까지 솟구쳤다가 내리꽂히면 화면 안의 물건이랑 벽까지 한꺼번에 박살 나!</t>
+          <t>언제 깨어날지는 아무도 몰라... 신비한 힘이니까! 찍!</t>
         </is>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3900055</v>
+        <v>3900056</v>
       </c>
       <c r="G58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>g_superjump</t>
+          <t>l_skill_pick</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>labrat</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -4707,21 +4771,25 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>언제 깨어날지는 아무도 몰라... 신비한 힘이니까! 찍!</t>
+          <t>치즈가 모였으니 바로 하나 찍어 보자! 반짝이는 이 칸을 눌러 봐!</t>
         </is>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3900056</v>
-      </c>
-      <c r="G59" s="4" t="n"/>
+        <v>3900057</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>skill_next</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>l_skill_pick</t>
+          <t>l_skill_poor</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4731,30 +4799,26 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>panic</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>치즈가 모였으니 바로 하나 찍어 보자! 반짝이는 이 칸을 눌러 봐!</t>
+          <t>어라, 지금 치즈로는 아직 못 찍겠네... 다음 판에서 치즈를 더 모아 오자!</t>
         </is>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3900057</v>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>skill_next</t>
-        </is>
-      </c>
+        <v>3900058</v>
+      </c>
+      <c r="G60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>l_skill_poor</t>
+          <t>l_skill_pick2</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4764,26 +4828,30 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>panic</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>어라, 지금 치즈로는 아직 못 찍겠네... 다음 판에서 치즈를 더 모아 오자!</t>
+          <t>치즈가 모였네! 이제 반짝이는 이 칸을 눌러서 스킬을 찍어 보자!</t>
         </is>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3900058</v>
-      </c>
-      <c r="G61" s="4" t="n"/>
+        <v>3900059</v>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>skill_next</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>l_skill_pick2</t>
+          <t>l_skill_buy</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4793,30 +4861,30 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>치즈가 모였네! 이제 반짝이는 이 칸을 눌러서 스킬을 찍어 보자!</t>
+          <t>좋아! 이제 이 '활성화' 버튼을 눌러! 치즈를 내면 스킬이 켜져.</t>
         </is>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3900059</v>
+        <v>3900060</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>skill_next</t>
+          <t>skill_buy</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>l_skill_buy</t>
+          <t>l_skill_done</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4826,26 +4894,22 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>좋아! 이제 이 '활성화' 버튼을 눌러! 치즈를 내면 스킬이 켜져.</t>
+          <t>해냈다! 다음 판부터 우리 쥐들이 더 강해질 거야!</t>
         </is>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3900060</v>
-      </c>
-      <c r="G63" s="4" t="inlineStr">
-        <is>
-          <t>skill_buy</t>
-        </is>
-      </c>
+        <v>3900061</v>
+      </c>
+      <c r="G63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
@@ -4859,26 +4923,26 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>해냈다! 다음 판부터 우리 쥐들이 더 강해질 거야!</t>
+          <t>치즈가 남으면 선으로 이어진 다음 칸도 계속 찍어 봐. 이어진 칸만 열 수 있어!</t>
         </is>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3900061</v>
+        <v>3900062</v>
       </c>
       <c r="G64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>l_skill_done</t>
+          <t>g_promote</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4888,22 +4952,22 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>치즈가 남으면 선으로 이어진 다음 칸도 계속 찍어 봐. 이어진 칸만 열 수 있어!</t>
+          <t>아, 그런데 조심해! 승급에 쓴 쥐들은 하나로 합쳐져서 사라져.</t>
         </is>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3900062</v>
+        <v>3900063</v>
       </c>
       <c r="G65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
@@ -4912,27 +4976,27 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>brownrat</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>panic</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>아, 그런데 조심해! 승급에 쓴 쥐들은 하나로 합쳐져서 사라져.</t>
+          <t>쥐가 너무 적어지면 서로 부딪힐 일이 줄어서 새끼가 거의 안 태어나!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
         </is>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3900063</v>
+        <v>3900064</v>
       </c>
       <c r="G66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
@@ -4941,64 +5005,64 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>brownrat</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>panic</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>쥐가 너무 적어지면 서로 부딪힐 일이 줄어서 새끼가 거의 안 태어나!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
+          <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
         </is>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3900064</v>
-      </c>
-      <c r="G67" s="4" t="n"/>
+        <v>3900065</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>g_promote</t>
+          <t>l_alley</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>brownrat</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
+          <t>찍?! 바닥 아래에서 위잉~ 하는 소리가 나!</t>
         </is>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3900065</v>
-      </c>
-      <c r="G68" s="4" t="inlineStr">
-        <is>
-          <t>promote</t>
-        </is>
-      </c>
+        <v>3900068</v>
+      </c>
+      <c r="G68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>g_power_promote_new</t>
+          <t>l_alley</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5008,26 +5072,30 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>panic</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>그런데 너무 많이 합치면 쥐가 적어져서 번식이 거의 안 돼!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
+          <t>바닥의 맨홀 뚜껑 아래에서 나는 소리야! 뚜껑을 눌러서 지하 하수구로 내려가 보자!</t>
         </is>
       </c>
       <c r="F69" s="4" t="n">
-        <v>3900066</v>
-      </c>
-      <c r="G69" s="4" t="n"/>
+        <v>3900069</v>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>alley_arrow</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>g_power_promote_new</t>
+          <t>l_gacha_hot</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -5037,64 +5105,68 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
+          <t>이거 봐! 연구소에서 버린 유전자 분석기를… 믹서기로 고쳐 놨어!</t>
         </is>
       </c>
       <c r="F70" s="4" t="n">
-        <v>3900065</v>
+        <v>3900070</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>promote</t>
+          <t>hot_gacha</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>l_alley</t>
+          <t>l_gacha_hot</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>brownrat</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>찍?! 바닥 아래에서 위잉~ 하는 소리가 나!</t>
+          <t>훔친 연구 자료를 넣으면 동료들의 유전자를 추출할 수 있어. 눌러서 열어 보자!</t>
         </is>
       </c>
       <c r="F71" s="4" t="n">
-        <v>3900068</v>
-      </c>
-      <c r="G71" s="4" t="n"/>
+        <v>3900071</v>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>hot_gacha</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>l_alley</t>
+          <t>l_gacha_page</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>brownrat</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -5104,25 +5176,21 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>바닥의 맨홀 뚜껑 아래에서 나는 소리야! 뚜껑을 눌러서 지하 하수구로 내려가 보자!</t>
+          <t>유전자 추출기야. 연구 자료를 내면 쥐 조각이 든 캡슐이 나와!</t>
         </is>
       </c>
       <c r="F72" s="4" t="n">
-        <v>3900069</v>
-      </c>
-      <c r="G72" s="4" t="inlineStr">
-        <is>
-          <t>alley_arrow</t>
-        </is>
-      </c>
+        <v>3900072</v>
+      </c>
+      <c r="G72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>l_gacha_hot</t>
+          <t>l_gacha_page</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -5137,54 +5205,50 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>이거 봐! 연구소에서 버린 유전자 분석기를… 믹서기로 고쳐 놨어!</t>
+          <t>처음 한 번은 10회 뽑기가 공짜야! 이 버튼부터 눌러 봐.</t>
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>3900070</v>
+        <v>3900073</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>hot_gacha</t>
+          <t>gacha_ten</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>l_gacha_hot</t>
+          <t>l_gacha_page</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>labrat</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>panic</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>훔친 연구 자료를 넣으면 동료들의 유전자를 추출할 수 있어. 눌러서 열어 보자!</t>
+          <t>잠깐… 믹서기에 우리가 들어가는 거야?! …괜찮은 거 맞지?</t>
         </is>
       </c>
       <c r="F74" s="4" t="n">
-        <v>3900071</v>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
-        <is>
-          <t>hot_gacha</t>
-        </is>
-      </c>
+        <v>3900074</v>
+      </c>
+      <c r="G74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
@@ -5203,17 +5267,21 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>유전자 추출기야. 연구 자료를 내면 쥐 조각이 든 캡슐이 나와!</t>
+          <t>10회 뽑기는 유니크 이상 하나가 꼭 나와. 그리고 전설이 30번, 신화가 100번 안 나오면 다음엔 무조건 나와!</t>
         </is>
       </c>
       <c r="F75" s="4" t="n">
-        <v>3900072</v>
-      </c>
-      <c r="G75" s="4" t="n"/>
+        <v>3900075</v>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>gacha_pity</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
@@ -5227,64 +5295,68 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>처음 한 번은 10회 뽑기가 공짜야! 이 버튼부터 눌러 봐.</t>
+          <t>확률은 여기 다 적어 놨어. 나온 조각은 쳇바퀴 훈련에서 바로 쓸 수 있어!</t>
         </is>
       </c>
       <c r="F76" s="4" t="n">
-        <v>3900073</v>
+        <v>3900076</v>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>gacha_ten</t>
+          <t>gacha_rates</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>l_gacha_page</t>
+          <t>l_market_lobby</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>labrat</t>
+          <t>brownrat</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>panic</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>잠깐… 믹서기에 우리가 들어가는 거야?! …괜찮은 거 맞지?</t>
+          <t>쉿… 맨홀 아래 하수구에서 누가 우리를 부르는데? 내려가 볼까?</t>
         </is>
       </c>
       <c r="F77" s="4" t="n">
-        <v>3900074</v>
-      </c>
-      <c r="G77" s="4" t="n"/>
+        <v>3900077</v>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>alley_arrow</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>l_gacha_page</t>
+          <t>l_market</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>broker</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -5294,91 +5366,87 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>10회 뽑기는 유니크 이상 하나가 꼭 나와. 그리고 전설이 30번, 신화가 100번 안 나오면 다음엔 무조건 나와!</t>
+          <t>어이~ 거기 쥐씨들. 이 몸은 연구소 지하 하수구의 브로커라고 해.</t>
         </is>
       </c>
       <c r="F78" s="4" t="n">
-        <v>3900075</v>
+        <v>3900078</v>
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>gacha_pity</t>
+          <t>hot_market</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>l_gacha_page</t>
+          <t>l_market</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>broker</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>확률은 여기 다 적어 놨어. 나온 조각은 쳇바퀴 훈련에서 바로 쓸 수 있어!</t>
+          <t>연구소에서 빼돌린 귀한 유전자 샘플이 있지. 치즈만 넉넉하면… 흐흐.</t>
         </is>
       </c>
       <c r="F79" s="4" t="n">
-        <v>3900076</v>
+        <v>3900079</v>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>gacha_rates</t>
+          <t>hot_market</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>l_market_lobby</t>
+          <t>l_market_page</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>brownrat</t>
+          <t>broker</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>쉿… 맨홀 아래 하수구에서 누가 우리를 부르는데? 내려가 볼까?</t>
+          <t>여긴 쥐구멍 암시장. 전설이랑 신화 쥐 조각만 취급한다고.</t>
         </is>
       </c>
       <c r="F80" s="4" t="n">
-        <v>3900077</v>
-      </c>
-      <c r="G80" s="4" t="inlineStr">
-        <is>
-          <t>alley_arrow</t>
-        </is>
-      </c>
+        <v>3900080</v>
+      </c>
+      <c r="G80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>l_market</t>
+          <t>l_market_page</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -5393,25 +5461,25 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>어이~ 거기 쥐씨들. 이 몸은 연구소 지하 하수구의 브로커라고 해.</t>
+          <t>값은 치즈로 받지. 물건마다 종이랑 수량이 다르니 잘 골라.</t>
         </is>
       </c>
       <c r="F81" s="4" t="n">
-        <v>3900078</v>
+        <v>3900081</v>
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>hot_market</t>
+          <t>market_slot</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>l_market</t>
+          <t>l_market_page</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -5426,21 +5494,21 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>연구소에서 빼돌린 귀한 유전자 샘플이 있지. 치즈만 넉넉하면… 흐흐.</t>
+          <t>탈출하면서 15분쯤 지나면 새 물건이 들어와. 기다리기 싫으면 치즈를 좀 더 내고 바로 바꿔 주지.</t>
         </is>
       </c>
       <c r="F82" s="4" t="n">
-        <v>3900079</v>
+        <v>3900082</v>
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>hot_market</t>
+          <t>market_reroll</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
@@ -5459,17 +5527,21 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>여긴 쥐구멍 암시장. 전설이랑 신화 쥐 조각만 취급한다고.</t>
+          <t>마음에 드는 물건은 자물쇠로 하나 잡아 둬. 바꿔도 그건 안 없어지니까.</t>
         </is>
       </c>
       <c r="F83" s="4" t="n">
-        <v>3900080</v>
-      </c>
-      <c r="G83" s="4" t="n"/>
+        <v>3900083</v>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>market_lock</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
@@ -5483,26 +5555,26 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>값은 치즈로 받지. 물건마다 종이랑 수량이 다르니 잘 골라.</t>
+          <t>신화가 한동안 안 들어오면… 이 몸이 어떻게든 구해 온다고. 약속하지!</t>
         </is>
       </c>
       <c r="F84" s="4" t="n">
-        <v>3900081</v>
+        <v>3900084</v>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>market_slot</t>
+          <t>market_pity</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
@@ -5521,149 +5593,145 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>탈출하면서 15분쯤 지나면 새 물건이 들어와. 기다리기 싫으면 치즈를 좀 더 내고 바로 바꿔 주지.</t>
+          <t>첫 거래 기념으로 선물 하나 주지. 앞으로 잘 부탁해, 흐흐.</t>
         </is>
       </c>
       <c r="F85" s="4" t="n">
-        <v>3900082</v>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>market_reroll</t>
-        </is>
-      </c>
+        <v>3900085</v>
+      </c>
+      <c r="G85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>l_market_page</t>
+          <t>l_wish</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>broker</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>마음에 드는 물건은 자물쇠로 하나 잡아 둬. 바꿔도 그건 안 없어지니까.</t>
+          <t>18층을 넘었더니 추출기를 조정할 수 있게 됐어!</t>
         </is>
       </c>
       <c r="F86" s="4" t="n">
-        <v>3900083</v>
-      </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>market_lock</t>
-        </is>
-      </c>
+        <v>3900086</v>
+      </c>
+      <c r="G86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>l_market_page</t>
+          <t>l_wish</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>broker</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>신화가 한동안 안 들어오면… 이 몸이 어떻게든 구해 온다고. 약속하지!</t>
+          <t>전설이랑 신화에서 원하는 친구를 하나씩 고르면, 그 등급이 나올 때 그 친구가 더 잘 나와!</t>
         </is>
       </c>
       <c r="F87" s="4" t="n">
-        <v>3900084</v>
+        <v>3900087</v>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>market_pity</t>
+          <t>gacha_wish</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>l_market_page</t>
+          <t>g_pop_f5</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>broker</t>
+          <t>brownrat</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>첫 거래 기념으로 선물 하나 주지. 앞으로 잘 부탁해, 흐흐.</t>
+          <t>벌써 5층이야! 그런데 쥐는 끝없이 늘어나는 게 아니래.</t>
         </is>
       </c>
       <c r="F88" s="4" t="n">
-        <v>3900085</v>
+        <v>3900088</v>
       </c>
       <c r="G88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>l_wish</t>
+          <t>g_pop_f5</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>brownrat</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>18층을 넘었더니 추출기를 조정할 수 있게 됐어!</t>
+          <t>오른쪽 위 숫자가 지금 쥐 수 / 최대 쥐 수야. 꽉 차면 더는 번식할 수 없어!</t>
         </is>
       </c>
       <c r="F89" s="4" t="n">
-        <v>3900086</v>
-      </c>
-      <c r="G89" s="4" t="n"/>
+        <v>3900051</v>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>pop</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>l_wish</t>
+          <t>g_pop_f5</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
@@ -5673,35 +5741,35 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>전설이랑 신화에서 원하는 친구를 하나씩 고르면, 그 등급이 나올 때 그 친구가 더 잘 나와!</t>
+          <t>그 대신 꽉 차면 더 강해지는 비밀 기술 '승급'을 알려 줄게! 일단 꽉 채워 보자 찍!</t>
         </is>
       </c>
       <c r="F90" s="4" t="n">
-        <v>3900087</v>
+        <v>3900090</v>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>gacha_wish</t>
+          <t>pop</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>g_pop_f5</t>
+          <t>g_super</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>brownrat</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -5711,59 +5779,59 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>벌써 5층이야! 그런데 쥐는 끝없이 늘어나는 게 아니래.</t>
+          <t>우와! 신화 친구가 필살기를 다섯 번이나 써서 힘이 넘쳐흘러!</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>3900088</v>
+        <v>3900092</v>
       </c>
       <c r="G91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>g_pop_f5</t>
+          <t>g_super</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>brownrat</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>오른쪽 위 숫자가 지금 쥐 수 / 최대 쥐 수야. 꽉 차면 더는 번식할 수 없어!</t>
+          <t>아래 반짝이는 '초필살기' 버튼을 눌러 봐! 종마다 한 판에 한 번뿐이야 찍!!</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>3900051</v>
+        <v>3900093</v>
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>pop</t>
+          <t>super</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>g_pop_f5</t>
+          <t>g_aug</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>hero</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -5773,25 +5841,25 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>꽉 찼을 땐 승급으로 쥐를 합치면 자리가 다시 생겨! 번식할 쥐만 남기고 나머지는 승급시키자!</t>
+          <t>여기서부턴 층을 넘을 때마다 '증강'을 하나 고를 수 있지! 마음에 드는 걸 골라라!</t>
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>3900090</v>
+        <v>3900094</v>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>promote</t>
+          <t>augpick</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>g_super</t>
+          <t>g_aug_manage</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
@@ -5801,26 +5869,30 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>우와! 신화 친구가 필살기를 다섯 번이나 써서 힘이 넘쳐흘러!</t>
+          <t>고른 증강은 이번 판 동안 슬롯에 끼워져서 바로 효과가 나! 슬롯은 5칸이야.</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>3900092</v>
-      </c>
-      <c r="G94" s="4" t="n"/>
+        <v>3900095</v>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>augbar</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>g_super</t>
+          <t>g_aug_manage</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
@@ -5830,35 +5902,35 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>아래 반짝이는 '초필살기' 버튼을 눌러 봐! 종마다 한 판에 한 번뿐이야 찍!!</t>
+          <t>얻은 증강은 전부 지하 '증강 연구소'에 쌓여! 판 중에도 Tab 을 누르면 보관함이랑 바꿔 낄 수 있어.</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>3900093</v>
+        <v>3900096</v>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>super</t>
+          <t>augbar</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>g_aug</t>
+          <t>l_aug</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>hero</t>
+          <t>broker</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -5868,30 +5940,30 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>여기서부턴 층을 넘을 때마다 '증강'을 하나 고를 수 있지! 마음에 드는 걸 골라라!</t>
+          <t>어이, 지하에 새 가게가 들어섰다구. 이름하여 '증강 연구소'!</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>3900094</v>
+        <v>3900097</v>
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>augpick</t>
+          <t>aug</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>g_aug_manage</t>
+          <t>l_aug</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>broker</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -5901,58 +5973,54 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>고른 증강은 이번 판 동안 슬롯에 끼워져서 바로 효과가 나! 슬롯은 5칸이야.</t>
+          <t>모은 증강을 구경하고, 같은 등급끼리 합성해서 더 좋은 놈을 노려 봐. 대신 꽝이 나올 수도 있다구?</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>3900095</v>
+        <v>3900098</v>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>augbar</t>
+          <t>aug</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>g_aug_manage</t>
+          <t>l_aug_page</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>nerd</t>
+          <t>broker</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>얻은 증강은 전부 지하 '증강 연구소'에 쌓여! 판 중에도 Tab 을 누르면 보관함이랑 바꿔 낄 수 있어.</t>
+          <t>판에서 끼고 층을 넘은 증강엔 강화 포인트가 쌓여. 포인트랑 치즈를 내면 효과가 조금씩 세진다구.</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>3900096</v>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>augbar</t>
-        </is>
-      </c>
+        <v>3900099</v>
+      </c>
+      <c r="G98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>l_aug</t>
+          <t>l_aug_page</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
@@ -5962,30 +6030,26 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>happy</t>
+          <t>surprised</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>어이, 지하에 새 가게가 들어섰다구. 이름하여 '증강 연구소'!</t>
+          <t>합성 재료로 쓴 증강은 강화도 같이 사라지니까 아끼는 놈은 조심하라구!</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>3900097</v>
-      </c>
-      <c r="G99" s="4" t="inlineStr">
-        <is>
-          <t>aug</t>
-        </is>
-      </c>
+        <v>3900100</v>
+      </c>
+      <c r="G99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>l_aug</t>
+          <t>l_aug_carry</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
@@ -6000,11 +6064,11 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>모은 증강을 구경하고, 같은 등급끼리 합성해서 더 좋은 놈을 노려 봐. 대신 꽝이 나올 수도 있다구?</t>
+          <t>41층까지 왔다고? 이제 연구소에서 증강 하나를 '들고 가기'로 정하면 1층부터 끼고 출발할 수 있다구!</t>
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>3900098</v>
+        <v>3900101</v>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
@@ -6014,16 +6078,16 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>l_aug_page</t>
+          <t>g_pop_promote</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>broker</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -6033,55 +6097,63 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>판에서 끼고 층을 넘은 증강엔 강화 포인트가 쌓여. 포인트랑 치즈를 내면 효과가 조금씩 세진다구.</t>
+          <t>걱정 마! 꽉 찼을 땐 '승급'을 쓰면 돼! 왼쪽 아래에 승급 버튼이 새로 생겼어!</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>3900099</v>
-      </c>
-      <c r="G101" s="4" t="n"/>
+        <v>3900102</v>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>l_aug_page</t>
+          <t>g_pop_promote</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>broker</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>surprised</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>합성 재료로 쓴 증강은 강화도 같이 사라지니까 아끼는 놈은 조심하라구!</t>
+          <t>같은 등급 쥐가 여럿 모이면 '승급'으로 더 높은 등급 쥐로 바꿀 수 있어.</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>3900100</v>
-      </c>
-      <c r="G102" s="4" t="n"/>
+        <v>3900010</v>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>l_aug_carry</t>
+          <t>g_pop_promote</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>broker</t>
+          <t>nerd</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -6091,15 +6163,106 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>41층까지 왔다고? 이제 연구소에서 증강 하나를 '들고 가기'로 정하면 1층부터 끼고 출발할 수 있다구!</t>
+          <t>합친 만큼 자리가 생겨서 다시 번식할 수 있고, 높은 등급 쥐는 힘도 훨씬 세다구! 왼쪽 아래 승급 버튼을 눌러 봐 찍!</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
-        <v>3900101</v>
+        <v>3900011</v>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>aug</t>
+          <t>promote</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_promote</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>아, 그런데 조심해! 승급에 쓴 쥐들은 하나로 합쳐져서 사라져.</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>3900063</v>
+      </c>
+      <c r="G104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_promote</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>panic</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>쥐가 너무 적어지면 서로 부딪힐 일이 줄어서 새끼가 거의 안 태어나!! 번식할 쥐는 꼭 남겨 둬 찍!</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>3900064</v>
+      </c>
+      <c r="G105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>g_pop_promote</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>승급 창의 '일괄 승급'은 번식할 쥐를 알아서 남겨 줘. 헷갈리면 그걸 눌러!</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>3900065</v>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>promote</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Step" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Line" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Story" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2870,6 +2870,106 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>g_meter</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>FloorTime</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>RunMin</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>g_power</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>meter</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>세 번째 판부터 층 시작 20초 뒤: 오른쪽 피해 순위(딜 미터기) 소개 · 해금</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>g_roster</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Game</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>After</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>g_meter</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>roster</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>딜 미터기 안내 바로 뒤: 쥐 목록 버튼(R) 소개 · 해금</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2881,7 +2981,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6102,6 +6202,163 @@
           <t>aug</t>
         </is>
       </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>g_meter</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>어? 오른쪽에 순위표가 생겼어!</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>3900102</v>
+      </c>
+      <c r="G104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>g_meter</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>이번 층에서 누가 제일 많이 부쉈는지 보여 주는 '피해 순위'야. 종마다 따로 세!</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>3900103</v>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>g_meter</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>앞지를 때마다 순위가 휙휙 바뀌니까, 누가 우리 무리의 에이스인지 지켜봐!</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>3900104</v>
+      </c>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>meter</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>g_roster</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>지금 우리 무리에 누가 몇 마리 있는지 궁금하면 '쥐 목록'을 눌러 봐! R 키로도 열려!</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>3900105</v>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>g_roster</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>등급순 · 마릿수순 · 피해순으로 볼 수 있어. 열어 둔 동안엔 게임이 잠깐 멈춰!</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>3900106</v>
+      </c>
+      <c r="G108" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7030,7 +7287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7178,6 +7435,30 @@
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>로비: 친구들!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>meter</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>게임: 피해 순위 (딜 미터기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>roster</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>게임: 쥐 목록 버튼 · R 키</t>
         </is>
       </c>
     </row>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -1342,7 +1342,7 @@
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>튜토리얼 라운드 + 첫 치즈 창고(l_first) 다음 판 시작: 우리 힘 · 적정 힘 (2026-10-15: 두 번째 판 → l_first 다음 판)</t>
+          <t>두 번째 판 첫 층: 찍찍!!(우리 힘) 표시 해금 · 설명 (적정은 화면에 안 보임, 2026-10-21)</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>지난번엔 아깝게 잡혀 버렸지... 이번엔 '적정 찍찍'을 알려 줄게!</t>
+          <t>지난번엔 아깝게 잡혀 버렸지... 이번엔 우리 힘을 보는 법을 알려 줄게!</t>
         </is>
       </c>
       <c r="F26" s="5" t="n">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>왼쪽 위 '찍찍!!' 숫자는 지금 우리 무리의 힘이고, 옆의 '적정'은 이 층을 넉넉히 깨려면 필요한 힘이야.</t>
+          <t>왼쪽 위 '찍찍!!' 숫자가 지금 우리 무리의 힘이야. 쥐가 많아지고 세질수록 쑥쑥 올라가!</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>panic</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>우리 힘이 적정보다 낮으면 시간 안에 계단까지 가기 힘들어!</t>
+          <t>위층일수록 벽도 단단해져. 막히면 찍찍!!을 더 키워서 다시 도전하자!</t>
         </is>
       </c>
       <c r="F28" s="5" t="n">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>적정 찍찍이 모자랄 땐 쥐를 최대 마릿수까지 꽉 채워 봐!</t>
+          <t>더 강해지고 싶을 땐 쥐를 최대 마릿수까지 꽉 채워 봐!</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -6534,7 +6534,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6570,6 +6570,11 @@
           <t>대사 키</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>컷씬 (비움 = 오프닝 · ending = 엔딩)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -6597,6 +6602,11 @@
           <t>text_sk</t>
         </is>
       </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -6622,6 +6632,11 @@
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>int</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -6875,6 +6890,188 @@
       </c>
       <c r="E15" s="5" t="n">
         <v>4000012</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>ending_01</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>찍...! (마지막 문이... 열렸어.)</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4000013</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>ending_01</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>찍찍! (그 너머엔 처음 보는 빛이 쏟아지고 있었어.)</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4000014</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>ending_02</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>찍찍찍!! (바깥이다!! 진짜 하늘이야!!)</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4000015</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>ending_03</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>찍~ (이제 손가락의 은총 같은 건 필요 없어.)</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4000016</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>ending_04</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>찍찍... (치즈는 이제 우리 힘으로 찾을 거야.)</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4000017</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>ending_04</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>찍!찍!!찍!!! (모두 함께라면 어디든 갈 수 있으니까!!)</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4000018</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>ending_05</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>찍...? (그런데... 저 멀리, 또 다른 연구소의 불빛이...)</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4000019</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ending</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Step" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Line" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Story" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Speaker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Step" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Line" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Story" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trigger_Type" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cond_Type" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unlock_Id" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action_Type" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Data_Table/튜토리얼 테이블.xlsx
+++ b/Data_Table/튜토리얼 테이블.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3034,6 +3034,98 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>TierAtLeast</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Unlocked</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>alley</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>arcade</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>10훈장 달고 아지트: 맨홀 아래 미니 게임기 등장 · 해금 (2026-10-30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade_hot</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Lobby</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>AlleyEnter</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade 뒤 뒷골목 도착: 미니 게임기 안내 (암시장 왼쪽)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3045,7 +3137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6522,6 +6614,167 @@
         <v>3900112</v>
       </c>
       <c r="G111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>113</v>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>어?! 맨홀 아래에서 뿅뿅 하는 소리가 나!</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>3900113</v>
+      </c>
+      <c r="G112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>114</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>brownrat</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>누가 뒷골목에 게임기를 들여놨나 봐! 맨홀로 내려가 보자!</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>3900114</v>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>alley_arrow</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>115</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade_hot</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>surprised</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>이건… 전설의 미니 게임기잖아! 10훈장을 단 쥐만 만질 수 있다는 그거!</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>3900115</v>
+      </c>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>arcade</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>116</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade_hot</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>nerd</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>판과 판 사이에 여기서 머리 좀 식혀 봐. 게임기를 누르면 미니게임을 할 수 있어!</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>3900116</v>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>arcade</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>117</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>l_arcade_hot</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>broker</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>흐흐, 고양이 연구소 휴게실에서 슬쩍한 물건이지. 공짜니까 실컷 놀다 가라고.</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>3900117</v>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>arcade</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7647,7 +7900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7819,6 +8072,18 @@
       <c r="B14" s="4" t="inlineStr">
         <is>
           <t>게임: 쥐 목록 버튼 · R 키</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>arcade</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>로비: 뒷골목 미니 게임기 (10훈장, l_arcade)</t>
         </is>
       </c>
     </row>
